--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nirmal" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amarai" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendors" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deeplaxmie Events" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nirmal's Executive" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Nirmal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Amarai" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vendors" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Deeplaxmie Events" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Nirmal's Executive" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Vendors'!$A$3:$Q$18</definedName>
@@ -2103,6 +2103,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="49">
       <c r="A3" s="12" t="inlineStr">
         <is>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -845,6 +845,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -896,6 +897,7 @@
         <v>37</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="48" t="inlineStr">
         <is>
@@ -986,6 +988,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="48" t="inlineStr">
         <is>
@@ -1043,7 +1046,11 @@
         </is>
       </c>
       <c r="B22" s="54" t="n"/>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Suraj Singh</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1207,7 +1207,11 @@
         </is>
       </c>
       <c r="B33" s="54" t="n"/>
-      <c r="C33" s="9" t="n"/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Randhir Singh</t>
+        </is>
+      </c>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="9" t="n"/>
@@ -1537,6 +1541,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -1600,6 +1605,7 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="48" t="inlineStr">
         <is>
@@ -1680,6 +1686,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="24" customHeight="1" s="49">
       <c r="A20" s="48" t="inlineStr">
         <is>
@@ -2214,7 +2221,7 @@
           <t>8605622211</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n"/>
+      <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
@@ -2241,13 +2248,13 @@
         <f>IF(I4="","",I4-IF(J4="",0,J4))</f>
         <v/>
       </c>
-      <c r="L4" s="14" t="n"/>
+      <c r="L4" s="14" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr">
         <is>
           <t>Invoice 284</t>
         </is>
       </c>
-      <c r="N4" s="18" t="n"/>
+      <c r="N4" s="18" t="inlineStr"/>
       <c r="O4" s="14">
         <f>IF(I4="","Not Quoted",IF(K4&lt;=0,"Paid","Pending"))</f>
         <v/>
@@ -2269,11 +2276,11 @@
           <t>Tent &amp; Banquet Hall</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="22" t="inlineStr"/>
+      <c r="D5" s="23" t="inlineStr"/>
       <c r="E5" s="24" t="n"/>
-      <c r="F5" s="25" t="n"/>
+      <c r="F5" s="25" t="inlineStr"/>
       <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Sangeet + Reception</t>
@@ -2290,15 +2297,15 @@
         <f>IF(I5="","",I5-IF(J5="",0,J5))</f>
         <v/>
       </c>
-      <c r="L5" s="24" t="n"/>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="30" t="n"/>
+      <c r="L5" s="24" t="inlineStr"/>
+      <c r="M5" s="21" t="inlineStr"/>
+      <c r="N5" s="30" t="inlineStr"/>
       <c r="O5" s="14">
         <f>IF(I5="","Not Quoted",IF(K5&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
+      <c r="Q5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -2306,32 +2313,32 @@
           <t>Flower Decoration</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="23" t="n"/>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr"/>
       <c r="E6" s="24" t="n"/>
-      <c r="F6" s="25" t="n"/>
+      <c r="F6" s="25" t="inlineStr"/>
       <c r="G6" s="26" t="inlineStr">
         <is>
           <t>All events</t>
         </is>
       </c>
-      <c r="H6" s="27" t="n"/>
+      <c r="H6" s="27" t="inlineStr"/>
       <c r="I6" s="28" t="n"/>
       <c r="J6" s="28" t="n"/>
       <c r="K6" s="29">
         <f>IF(I6="","",I6-IF(J6="",0,J6))</f>
         <v/>
       </c>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="21" t="n"/>
-      <c r="N6" s="30" t="n"/>
+      <c r="L6" s="24" t="inlineStr"/>
+      <c r="M6" s="21" t="inlineStr"/>
+      <c r="N6" s="30" t="inlineStr"/>
       <c r="O6" s="27">
         <f>IF(I6="","Not Quoted",IF(K6&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P6" s="25" t="n"/>
-      <c r="Q6" s="25" t="n"/>
+      <c r="Q6" s="25" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -2339,11 +2346,11 @@
           <t>Photography</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="23" t="n"/>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr"/>
       <c r="E7" s="24" t="n"/>
-      <c r="F7" s="25" t="n"/>
+      <c r="F7" s="25" t="inlineStr"/>
       <c r="G7" s="26" t="inlineStr">
         <is>
           <t>Wedding</t>
@@ -2360,15 +2367,15 @@
         <f>IF(I7="","",I7-IF(J7="",0,J7))</f>
         <v/>
       </c>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="30" t="n"/>
+      <c r="L7" s="24" t="inlineStr"/>
+      <c r="M7" s="21" t="inlineStr"/>
+      <c r="N7" s="30" t="inlineStr"/>
       <c r="O7" s="27">
         <f>IF(I7="","Not Quoted",IF(K7&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="25" t="n"/>
+      <c r="Q7" s="25" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2376,11 +2383,11 @@
           <t>Videography</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="23" t="n"/>
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="22" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr"/>
       <c r="E8" s="24" t="n"/>
-      <c r="F8" s="25" t="n"/>
+      <c r="F8" s="25" t="inlineStr"/>
       <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Wedding</t>
@@ -2397,15 +2404,15 @@
         <f>IF(I8="","",I8-IF(J8="",0,J8))</f>
         <v/>
       </c>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="30" t="n"/>
+      <c r="L8" s="24" t="inlineStr"/>
+      <c r="M8" s="21" t="inlineStr"/>
+      <c r="N8" s="30" t="inlineStr"/>
       <c r="O8" s="14">
         <f>IF(I8="","Not Quoted",IF(K8&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P8" s="25" t="n"/>
-      <c r="Q8" s="25" t="n"/>
+      <c r="Q8" s="25" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
@@ -2413,11 +2420,11 @@
           <t>Catering (Food)</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="23" t="n"/>
+      <c r="B9" s="21" t="inlineStr"/>
+      <c r="C9" s="22" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr"/>
       <c r="E9" s="24" t="n"/>
-      <c r="F9" s="25" t="n"/>
+      <c r="F9" s="25" t="inlineStr"/>
       <c r="G9" s="26" t="inlineStr">
         <is>
           <t>Sangeet, Reception, Brunch</t>
@@ -2434,15 +2441,15 @@
         <f>IF(I9="","",I9-IF(J9="",0,J9))</f>
         <v/>
       </c>
-      <c r="L9" s="24" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="30" t="n"/>
+      <c r="L9" s="24" t="inlineStr"/>
+      <c r="M9" s="21" t="inlineStr"/>
+      <c r="N9" s="30" t="inlineStr"/>
       <c r="O9" s="27">
         <f>IF(I9="","Not Quoted",IF(K9&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P9" s="25" t="n"/>
-      <c r="Q9" s="25" t="n"/>
+      <c r="Q9" s="25" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2450,11 +2457,11 @@
           <t>Pandit / Purohit</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="23" t="n"/>
+      <c r="B10" s="21" t="inlineStr"/>
+      <c r="C10" s="22" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr"/>
       <c r="E10" s="24" t="n"/>
-      <c r="F10" s="25" t="n"/>
+      <c r="F10" s="25" t="inlineStr"/>
       <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Wedding Ceremony</t>
@@ -2471,15 +2478,15 @@
         <f>IF(I10="","",I10-IF(J10="",0,J10))</f>
         <v/>
       </c>
-      <c r="L10" s="24" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="30" t="n"/>
+      <c r="L10" s="24" t="inlineStr"/>
+      <c r="M10" s="21" t="inlineStr"/>
+      <c r="N10" s="30" t="inlineStr"/>
       <c r="O10" s="14">
         <f>IF(I10="","Not Quoted",IF(K10&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P10" s="25" t="n"/>
-      <c r="Q10" s="25" t="n"/>
+      <c r="Q10" s="25" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
@@ -2487,11 +2494,11 @@
           <t>Makeup &amp; Mehendi</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="23" t="n"/>
+      <c r="B11" s="21" t="inlineStr"/>
+      <c r="C11" s="22" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr"/>
       <c r="E11" s="24" t="n"/>
-      <c r="F11" s="25" t="n"/>
+      <c r="F11" s="25" t="inlineStr"/>
       <c r="G11" s="26" t="inlineStr">
         <is>
           <t>Mehendi</t>
@@ -2508,15 +2515,15 @@
         <f>IF(I11="","",I11-IF(J11="",0,J11))</f>
         <v/>
       </c>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="30" t="n"/>
+      <c r="L11" s="24" t="inlineStr"/>
+      <c r="M11" s="21" t="inlineStr"/>
+      <c r="N11" s="30" t="inlineStr"/>
       <c r="O11" s="27">
         <f>IF(I11="","Not Quoted",IF(K11&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P11" s="25" t="n"/>
-      <c r="Q11" s="25" t="n"/>
+      <c r="Q11" s="25" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2524,11 +2531,11 @@
           <t>Stage &amp; Seating</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="23" t="n"/>
+      <c r="B12" s="21" t="inlineStr"/>
+      <c r="C12" s="22" t="inlineStr"/>
+      <c r="D12" s="23" t="inlineStr"/>
       <c r="E12" s="24" t="n"/>
-      <c r="F12" s="25" t="n"/>
+      <c r="F12" s="25" t="inlineStr"/>
       <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Sangeet + Wedding</t>
@@ -2545,15 +2552,15 @@
         <f>IF(I12="","",I12-IF(J12="",0,J12))</f>
         <v/>
       </c>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="30" t="n"/>
+      <c r="L12" s="24" t="inlineStr"/>
+      <c r="M12" s="21" t="inlineStr"/>
+      <c r="N12" s="30" t="inlineStr"/>
       <c r="O12" s="14">
         <f>IF(I12="","Not Quoted",IF(K12&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P12" s="25" t="n"/>
-      <c r="Q12" s="25" t="n"/>
+      <c r="Q12" s="25" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -2561,11 +2568,11 @@
           <t>Transport / Cars</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="23" t="n"/>
+      <c r="B13" s="21" t="inlineStr"/>
+      <c r="C13" s="22" t="inlineStr"/>
+      <c r="D13" s="23" t="inlineStr"/>
       <c r="E13" s="24" t="n"/>
-      <c r="F13" s="25" t="n"/>
+      <c r="F13" s="25" t="inlineStr"/>
       <c r="G13" s="26" t="inlineStr">
         <is>
           <t>Baraat</t>
@@ -2582,15 +2589,15 @@
         <f>IF(I13="","",I13-IF(J13="",0,J13))</f>
         <v/>
       </c>
-      <c r="L13" s="24" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="30" t="n"/>
+      <c r="L13" s="24" t="inlineStr"/>
+      <c r="M13" s="21" t="inlineStr"/>
+      <c r="N13" s="30" t="inlineStr"/>
       <c r="O13" s="27">
         <f>IF(I13="","Not Quoted",IF(K13&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P13" s="25" t="n"/>
-      <c r="Q13" s="25" t="n"/>
+      <c r="Q13" s="25" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2598,11 +2605,11 @@
           <t>Return Gifts / Favours</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="23" t="n"/>
+      <c r="B14" s="21" t="inlineStr"/>
+      <c r="C14" s="22" t="inlineStr"/>
+      <c r="D14" s="23" t="inlineStr"/>
       <c r="E14" s="24" t="n"/>
-      <c r="F14" s="25" t="n"/>
+      <c r="F14" s="25" t="inlineStr"/>
       <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Reception</t>
@@ -2619,15 +2626,15 @@
         <f>IF(I14="","",I14-IF(J14="",0,J14))</f>
         <v/>
       </c>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="30" t="n"/>
+      <c r="L14" s="24" t="inlineStr"/>
+      <c r="M14" s="21" t="inlineStr"/>
+      <c r="N14" s="30" t="inlineStr"/>
       <c r="O14" s="14">
         <f>IF(I14="","Not Quoted",IF(K14&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P14" s="25" t="n"/>
-      <c r="Q14" s="25" t="n"/>
+      <c r="Q14" s="25" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
@@ -2635,11 +2642,11 @@
           <t>Haldi &amp; Mehendi Items</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="23" t="n"/>
+      <c r="B15" s="21" t="inlineStr"/>
+      <c r="C15" s="22" t="inlineStr"/>
+      <c r="D15" s="23" t="inlineStr"/>
       <c r="E15" s="24" t="n"/>
-      <c r="F15" s="25" t="n"/>
+      <c r="F15" s="25" t="inlineStr"/>
       <c r="G15" s="26" t="inlineStr">
         <is>
           <t>Haldi</t>
@@ -2656,15 +2663,15 @@
         <f>IF(I15="","",I15-IF(J15="",0,J15))</f>
         <v/>
       </c>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="30" t="n"/>
+      <c r="L15" s="24" t="inlineStr"/>
+      <c r="M15" s="21" t="inlineStr"/>
+      <c r="N15" s="30" t="inlineStr"/>
       <c r="O15" s="27">
         <f>IF(I15="","Not Quoted",IF(K15&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P15" s="25" t="n"/>
-      <c r="Q15" s="25" t="n"/>
+      <c r="Q15" s="25" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2672,11 +2679,11 @@
           <t>Sangeet Anchoring / Choreography</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="23" t="n"/>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="22" t="inlineStr"/>
+      <c r="D16" s="23" t="inlineStr"/>
       <c r="E16" s="24" t="n"/>
-      <c r="F16" s="25" t="n"/>
+      <c r="F16" s="25" t="inlineStr"/>
       <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Sangeet Night</t>
@@ -2693,15 +2700,15 @@
         <f>IF(I16="","",I16-IF(J16="",0,J16))</f>
         <v/>
       </c>
-      <c r="L16" s="24" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="30" t="n"/>
+      <c r="L16" s="24" t="inlineStr"/>
+      <c r="M16" s="21" t="inlineStr"/>
+      <c r="N16" s="30" t="inlineStr"/>
       <c r="O16" s="14">
         <f>IF(I16="","Not Quoted",IF(K16&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P16" s="25" t="n"/>
-      <c r="Q16" s="25" t="n"/>
+      <c r="Q16" s="25" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2709,28 +2716,28 @@
           <t>Other / Miscellaneous</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="23" t="n"/>
+      <c r="B17" s="21" t="inlineStr"/>
+      <c r="C17" s="22" t="inlineStr"/>
+      <c r="D17" s="23" t="inlineStr"/>
       <c r="E17" s="24" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="14" t="n"/>
+      <c r="F17" s="25" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
       <c r="I17" s="28" t="n"/>
       <c r="J17" s="28" t="n"/>
       <c r="K17" s="17">
         <f>IF(I17="","",I17-IF(J17="",0,J17))</f>
         <v/>
       </c>
-      <c r="L17" s="24" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="30" t="n"/>
+      <c r="L17" s="24" t="inlineStr"/>
+      <c r="M17" s="21" t="inlineStr"/>
+      <c r="N17" s="30" t="inlineStr"/>
       <c r="O17" s="14">
         <f>IF(I17="","Not Quoted",IF(K17&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P17" s="25" t="n"/>
-      <c r="Q17" s="25" t="n"/>
+      <c r="Q17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="75" customHeight="1" s="49">
       <c r="A18" s="38" t="inlineStr">
@@ -2750,7 +2757,7 @@
       </c>
       <c r="D18" s="57" t="inlineStr">
         <is>
-          <t>‪+91 93091 74167‬</t>
+          <t>+91?93091?74167</t>
         </is>
       </c>
       <c r="E18" s="24" t="n"/>
@@ -2764,7 +2771,7 @@
           <t>Accommodation 08-14 Dec</t>
         </is>
       </c>
-      <c r="H18" s="16" t="n"/>
+      <c r="H18" s="16" t="inlineStr"/>
       <c r="I18" s="14" t="n">
         <v>84000</v>
       </c>
@@ -2775,15 +2782,15 @@
         <f>IF(I18="","",I18-IF(J18="",0,J18))</f>
         <v/>
       </c>
-      <c r="L18" s="17" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
+      <c r="L18" s="17" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+      <c r="N18" s="14" t="inlineStr"/>
       <c r="O18" s="18">
         <f>IF(I18="","Not Quoted",IF(K18&lt;=0,"Paid","Pending"))</f>
         <v/>
       </c>
       <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="46" t="n"/>
+      <c r="Q18" s="46" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1051,7 +1051,11 @@
           <t>Suraj Singh</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Raghavendra</t>
+        </is>
+      </c>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -845,7 +845,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -897,7 +896,6 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="48" t="inlineStr">
         <is>
@@ -988,7 +986,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="48" t="inlineStr">
         <is>
@@ -1545,7 +1542,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -1609,7 +1605,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="48" t="inlineStr">
         <is>
@@ -1690,7 +1685,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="24" customHeight="1" s="49">
       <c r="A20" s="48" t="inlineStr">
         <is>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -845,6 +845,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -896,6 +897,7 @@
         <v>37</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="48" t="inlineStr">
         <is>
@@ -986,6 +988,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="48" t="inlineStr">
         <is>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1046,11 +1046,7 @@
         </is>
       </c>
       <c r="B22" s="54" t="n"/>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Suraj Singh</t>
-        </is>
-      </c>
+      <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Raghavendra</t>
@@ -1211,11 +1207,7 @@
         </is>
       </c>
       <c r="B33" s="54" t="n"/>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Randhir Singh</t>
-        </is>
-      </c>
+      <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1047,11 +1047,7 @@
       </c>
       <c r="B22" s="54" t="n"/>
       <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Raghavendra</t>
-        </is>
-      </c>
+      <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1426,6 +1426,7 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="50" t="inlineStr">
         <is>
@@ -1533,6 +1534,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -1596,6 +1598,7 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="48" t="inlineStr">
         <is>
@@ -1676,6 +1679,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="24" customHeight="1" s="49">
       <c r="A20" s="48" t="inlineStr">
         <is>
@@ -1996,6 +2000,7 @@
         <v/>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="50" t="inlineStr">
         <is>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -822,16 +822,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:AH64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="49" min="1" max="1"/>
-    <col width="15" customWidth="1" style="49" min="2" max="7"/>
-    <col width="34" customWidth="1" style="49" min="8" max="8"/>
-    <col width="15" customWidth="1" style="49" min="9" max="12"/>
+    <col width="30" customWidth="1" style="49" min="1" max="1"/>
+    <col width="11" customWidth="1" style="49" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="49">
+    <row r="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
           <t>NIRMAL — ROOM PLAN BY NIGHT</t>
@@ -841,11 +839,10 @@
     <row r="2">
       <c r="A2" s="51" t="inlineStr">
         <is>
-          <t>Check-in 08-Dec-2026  |  Check-out 14-Dec-2026  |  10 rooms peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Check-in 08-Dec-2026  |  Check-out 14-Dec-2026  |  10 of 10 rooms booked</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -880,7 +877,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Total rooms</t>
+          <t>Rooms booked</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -890,333 +887,310 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Total rooms</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Total room-nights</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>ROOMS NEEDED PER NIGHT</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" s="49">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>08-Dec</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>08-Dec</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>09-Dec</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>10-Dec</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B15" s="4" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>11-Dec</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>12-Dec</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>12-Dec</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>13-Dec</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B18" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(B12:B17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="B19" s="5">
+        <f>SUM(B13:B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>ROOM ALLOCATION GRID</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" s="49">
-      <c r="A21" s="56" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>Room no.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>08-Dec-2026</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>09-Dec-2026</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>10-Dec-2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>11-Dec-2026</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>12-Dec-2026</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>13-Dec-2026</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t>Room 1 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Room 2 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B23" s="54" t="n"/>
+          <t>Room 1 - Guest 1</t>
+        </is>
+      </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
         <is>
-          <t>Room 3 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B24" s="54" t="n"/>
+          <t>Room 2 - Guest 1</t>
+        </is>
+      </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n"/>
-      <c r="I24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Room 4 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B25" s="54" t="n"/>
+          <t>Room 3 - Guest 1</t>
+        </is>
+      </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
         <is>
-          <t>Room 5 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B26" s="54" t="n"/>
+          <t>Room 4 - Guest 1</t>
+        </is>
+      </c>
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
       <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n"/>
-      <c r="I26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Room 6 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B27" s="54" t="n"/>
+          <t>Room 5 - Guest 1</t>
+        </is>
+      </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
         <is>
-          <t>Room 7 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B28" s="54" t="n"/>
+          <t>Room 6 - Guest 1</t>
+        </is>
+      </c>
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Room 8 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B29" s="54" t="n"/>
+          <t>Room 7 - Guest 1</t>
+        </is>
+      </c>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n"/>
-      <c r="I29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
         <is>
-          <t>Room 9 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B30" s="54" t="n"/>
+          <t>Room 8 - Guest 1</t>
+        </is>
+      </c>
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="9" t="n"/>
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
-      <c r="I30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Room 10 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B31" s="54" t="n"/>
+          <t>Room 9 - Guest 1</t>
+        </is>
+      </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="9" t="n"/>
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
-      <c r="I31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
-        <is>
-          <t>SECOND GUEST PER ROOM  -  only fill this block if two people share the room. FILLED counts occupied ROOMS, not guest names.</t>
-        </is>
-      </c>
+      <c r="A32" s="53" t="inlineStr">
+        <is>
+          <t>Room 10 - Guest 1</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
-        <is>
-          <t>Room 1 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B33" s="54" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>SECOND GUEST PER ROOM  -  fill only if two people share the room. FILLED counts occupied ROOMS, not guest names.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="53" t="inlineStr">
         <is>
-          <t>Room 2 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B34" s="54" t="n"/>
+          <t>Room 1 - Guest 2</t>
+        </is>
+      </c>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
@@ -1227,10 +1201,9 @@
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Room 3 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B35" s="54" t="n"/>
+          <t>Room 2 - Guest 2</t>
+        </is>
+      </c>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
@@ -1238,13 +1211,12 @@
       <c r="G35" s="9" t="n"/>
       <c r="H35" s="9" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1" s="49">
+    <row r="36">
       <c r="A36" s="53" t="inlineStr">
         <is>
-          <t>Room 4 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B36" s="54" t="n"/>
+          <t>Room 3 - Guest 2</t>
+        </is>
+      </c>
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
@@ -1252,13 +1224,12 @@
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1" s="49">
+    <row r="37">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Room 5 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B37" s="54" t="n"/>
+          <t>Room 4 - Guest 2</t>
+        </is>
+      </c>
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
@@ -1266,13 +1237,12 @@
       <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
     </row>
-    <row r="38" ht="24" customHeight="1" s="49">
+    <row r="38">
       <c r="A38" s="53" t="inlineStr">
         <is>
-          <t>Room 6 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B38" s="54" t="n"/>
+          <t>Room 5 - Guest 2</t>
+        </is>
+      </c>
       <c r="C38" s="9" t="n"/>
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
@@ -1280,13 +1250,12 @@
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="9" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1" s="49">
+    <row r="39">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Room 7 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B39" s="54" t="n"/>
+          <t>Room 6 - Guest 2</t>
+        </is>
+      </c>
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
@@ -1297,10 +1266,9 @@
     <row r="40">
       <c r="A40" s="53" t="inlineStr">
         <is>
-          <t>Room 8 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B40" s="54" t="n"/>
+          <t>Room 7 - Guest 2</t>
+        </is>
+      </c>
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
@@ -1311,10 +1279,9 @@
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Room 9 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B41" s="54" t="n"/>
+          <t>Room 8 - Guest 2</t>
+        </is>
+      </c>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="9" t="n"/>
       <c r="E41" s="9" t="n"/>
@@ -1325,10 +1292,9 @@
     <row r="42">
       <c r="A42" s="53" t="inlineStr">
         <is>
-          <t>Room 10 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B42" s="54" t="n"/>
+          <t>Room 9 - Guest 2</t>
+        </is>
+      </c>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
@@ -1337,170 +1303,344 @@
       <c r="H42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="55" t="inlineStr">
+      <c r="A43" s="53" t="inlineStr">
+        <is>
+          <t>Room 10 - Guest 2</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="inlineStr">
+        <is>
+          <t>THIRD GUEST PER ROOM  -  fill only if a THIRD person shares the room. These are the extra guests the hotel bills on top of the room rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="53" t="inlineStr">
+        <is>
+          <t>Room 1 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="53" t="inlineStr">
+        <is>
+          <t>Room 2 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="53" t="inlineStr">
+        <is>
+          <t>Room 3 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="53" t="inlineStr">
+        <is>
+          <t>Room 4 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="53" t="inlineStr">
+        <is>
+          <t>Room 5 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="53" t="inlineStr">
+        <is>
+          <t>Room 6 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="53" t="inlineStr">
+        <is>
+          <t>Room 7 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="53" t="inlineStr">
+        <is>
+          <t>Room 8 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="53" t="inlineStr">
+        <is>
+          <t>Room 9 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="53" t="inlineStr">
+        <is>
+          <t>Room 10 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="55" t="inlineStr">
         <is>
           <t>FILLED</t>
         </is>
       </c>
-      <c r="B43" s="54" t="n"/>
-      <c r="C43" s="11">
-        <f>SUMPRODUCT(--(((C22:C31&lt;&gt;"")+(C33:C42&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
-        <f>SUMPRODUCT(--(((D22:D31&lt;&gt;"")+(D33:D42&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="E43" s="11">
-        <f>SUMPRODUCT(--(((E22:E31&lt;&gt;"")+(E33:E42&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="F43" s="11">
-        <f>SUMPRODUCT(--(((F22:F31&lt;&gt;"")+(F33:F42&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>SUMPRODUCT(--(((G22:G31&lt;&gt;"")+(G33:G42&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="H43" s="11">
-        <f>SUMPRODUCT(--(((H22:H31&lt;&gt;"")+(H33:H42&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="55" t="inlineStr">
+      <c r="C55" s="11">
+        <f>SUMPRODUCT(--(((C23:C32&lt;&gt;"")+(C34:C43&lt;&gt;"")+(C45:C54&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="D55" s="11">
+        <f>SUMPRODUCT(--(((D23:D32&lt;&gt;"")+(D34:D43&lt;&gt;"")+(D45:D54&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="E55" s="11">
+        <f>SUMPRODUCT(--(((E23:E32&lt;&gt;"")+(E34:E43&lt;&gt;"")+(E45:E54&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="F55" s="11">
+        <f>SUMPRODUCT(--(((F23:F32&lt;&gt;"")+(F34:F43&lt;&gt;"")+(F45:F54&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="G55" s="11">
+        <f>SUMPRODUCT(--(((G23:G32&lt;&gt;"")+(G34:G43&lt;&gt;"")+(G45:G54&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="H55" s="11">
+        <f>SUMPRODUCT(--(((H23:H32&lt;&gt;"")+(H34:H43&lt;&gt;"")+(H45:H54&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="55" t="inlineStr">
         <is>
           <t>NEEDED</t>
         </is>
       </c>
-      <c r="B44" s="54" t="n"/>
-      <c r="C44" s="11" t="n">
+      <c r="C56" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D56" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E56" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F56" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G56" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H44" s="11" t="n">
+      <c r="H56" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="55" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="55" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="B45" s="54" t="n"/>
-      <c r="C45" s="4">
-        <f>IF(C43=C44,"OK",IF(C43&lt;C44,"need "&amp;(C44-C43)&amp;" more","extra "&amp;(C43-C44)))</f>
-        <v/>
-      </c>
-      <c r="D45" s="4">
-        <f>IF(D43=D44,"OK",IF(D43&lt;D44,"need "&amp;(D44-D43)&amp;" more","extra "&amp;(D43-D44)))</f>
-        <v/>
-      </c>
-      <c r="E45" s="4">
-        <f>IF(E43=E44,"OK",IF(E43&lt;E44,"need "&amp;(E44-E43)&amp;" more","extra "&amp;(E43-E44)))</f>
-        <v/>
-      </c>
-      <c r="F45" s="4">
-        <f>IF(F43=F44,"OK",IF(F43&lt;F44,"need "&amp;(F44-F43)&amp;" more","extra "&amp;(F43-F44)))</f>
-        <v/>
-      </c>
-      <c r="G45" s="4">
-        <f>IF(G43=G44,"OK",IF(G43&lt;G44,"need "&amp;(G44-G43)&amp;" more","extra "&amp;(G43-G44)))</f>
-        <v/>
-      </c>
-      <c r="H45" s="4">
-        <f>IF(H43=H44,"OK",IF(H43&lt;H44,"need "&amp;(H44-H43)&amp;" more","extra "&amp;(H43-H44)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="50" t="inlineStr">
+      <c r="C57">
+        <f>IF(C55=C56,"OK",IF(C55&lt;C56,"need "&amp;(C56-C55)&amp;" more","extra "&amp;(C55-C56)))</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IF(D55=D56,"OK",IF(D55&lt;D56,"need "&amp;(D56-D55)&amp;" more","extra "&amp;(D55-D56)))</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IF(E55=E56,"OK",IF(E55&lt;E56,"need "&amp;(E56-E55)&amp;" more","extra "&amp;(E55-E56)))</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF(F55=F56,"OK",IF(F55&lt;F56,"need "&amp;(F56-F55)&amp;" more","extra "&amp;(F55-F56)))</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>IF(G55=G56,"OK",IF(G55&lt;G56,"need "&amp;(G56-G55)&amp;" more","extra "&amp;(G55-G56)))</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>IF(H55=H56,"OK",IF(H55&lt;H56,"need "&amp;(H56-H55)&amp;" more","extra "&amp;(H55-H56)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="55" t="inlineStr">
+        <is>
+          <t>GUESTS</t>
+        </is>
+      </c>
+      <c r="C58" s="11">
+        <f>SUMPRODUCT(--(C23:C32&lt;&gt;""))+SUMPRODUCT(--(C34:C43&lt;&gt;""))+SUMPRODUCT(--(C45:C54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D58" s="11">
+        <f>SUMPRODUCT(--(D23:D32&lt;&gt;""))+SUMPRODUCT(--(D34:D43&lt;&gt;""))+SUMPRODUCT(--(D45:D54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="E58" s="11">
+        <f>SUMPRODUCT(--(E23:E32&lt;&gt;""))+SUMPRODUCT(--(E34:E43&lt;&gt;""))+SUMPRODUCT(--(E45:E54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="F58" s="11">
+        <f>SUMPRODUCT(--(F23:F32&lt;&gt;""))+SUMPRODUCT(--(F34:F43&lt;&gt;""))+SUMPRODUCT(--(F45:F54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G58" s="11">
+        <f>SUMPRODUCT(--(G23:G32&lt;&gt;""))+SUMPRODUCT(--(G34:G43&lt;&gt;""))+SUMPRODUCT(--(G45:G54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="H58" s="11">
+        <f>SUMPRODUCT(--(H23:H32&lt;&gt;""))+SUMPRODUCT(--(H34:H43&lt;&gt;""))+SUMPRODUCT(--(H45:H54&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="55" t="inlineStr">
+        <is>
+          <t>3rd GUESTS</t>
+        </is>
+      </c>
+      <c r="C59" s="11">
+        <f>SUMPRODUCT(--(C45:C54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D59" s="11">
+        <f>SUMPRODUCT(--(D45:D54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="E59" s="11">
+        <f>SUMPRODUCT(--(E45:E54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="F59" s="11">
+        <f>SUMPRODUCT(--(F45:F54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G59" s="11">
+        <f>SUMPRODUCT(--(G45:G54&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="H59" s="11">
+        <f>SUMPRODUCT(--(H45:H54&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="50" t="inlineStr">
         <is>
           <t>How to use:  every room has a 'Guest 1' row and a 'Guest 2' row. Type a name in the white cell for the night that guest is staying. Leave a cell blank if that guest is not in that room that night. FILLED counts occupied ROOMS, not guest names, so a room with two guests still counts as one room.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="50" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="50" t="inlineStr">
         <is>
           <t>Give this grid to the front desk on arrival. Hand out room keys against the names you typed.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="50" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="50" t="inlineStr">
         <is>
           <t>Two guests in one room?  Put the first name in the 'Guest 1' row and the second in the 'Guest 2' row for that same night. Both rows belong to the same room, so it still counts as one room against NEEDED.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="50" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="50" t="inlineStr">
         <is>
           <t>Check-out is 14-Dec-2026. 13-Dec is the last night and only 2 rooms are needed, so release the other 8 rooms after checkout on 13-Dec.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A34:B34"/>
+  <mergeCells count="9">
+    <mergeCell ref="A21:AH21"/>
+    <mergeCell ref="A63:AH63"/>
+    <mergeCell ref="A64:AH64"/>
+    <mergeCell ref="A33:AH33"/>
+    <mergeCell ref="A11:AH11"/>
+    <mergeCell ref="A44:AH44"/>
+    <mergeCell ref="A61:AH61"/>
+    <mergeCell ref="A4:AH4"/>
+    <mergeCell ref="A62:AH62"/>
   </mergeCells>
-  <conditionalFormatting sqref="C45:H45">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("need",C34))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>ISNUMBER(SEARCH("over",C34))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1511,16 +1651,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:AG56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="49" min="1" max="1"/>
-    <col width="15" customWidth="1" style="49" min="2" max="5"/>
-    <col width="34" customWidth="1" style="49" min="6" max="6"/>
-    <col width="15" customWidth="1" style="49" min="7" max="12"/>
+    <col width="30" customWidth="1" style="49" min="1" max="1"/>
+    <col width="11" customWidth="1" style="49" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="49">
+    <row r="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
           <t>AMARAI — ROOM PLAN BY NIGHT</t>
@@ -1530,11 +1668,10 @@
     <row r="2">
       <c r="A2" s="51" t="inlineStr">
         <is>
-          <t>Check-in 08-Dec-2026  |  Check-out 12-Dec-2026 at 12:30 PM  |  7 rooms peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Check-in 08-Dec-2026  |  Check-out 12-Dec-2026  |  7 of 7 rooms booked</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -1581,7 +1718,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Total rooms</t>
+          <t>Rooms booked</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1591,330 +1728,309 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Total rooms</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>Total room-nights</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>ROOMS NEEDED PER NIGHT</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" s="49">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>08-Dec</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>09-Dec</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B15" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>10-Dec</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>11-Dec</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B17" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>12-Dec</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B18" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(B13:B17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20" ht="24" customHeight="1" s="49">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="B19" s="5">
+        <f>SUM(B14:B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>ROOM ALLOCATION GRID</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="56" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>Room no.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>08-Dec-2026</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>09-Dec-2026</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>10-Dec-2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>11-Dec-2026</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>12-Dec-2026</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t>Room 1 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Room 2 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B23" s="54" t="n"/>
+          <t>Room 1 - Guest 1</t>
+        </is>
+      </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
-      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
         <is>
-          <t>Room 3 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B24" s="54" t="n"/>
+          <t>Room 2 - Guest 1</t>
+        </is>
+      </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
-      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Room 4 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B25" s="54" t="n"/>
+          <t>Room 3 - Guest 1</t>
+        </is>
+      </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
         <is>
-          <t>Room 5 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B26" s="54" t="n"/>
+          <t>Room 4 - Guest 1</t>
+        </is>
+      </c>
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
       <c r="G26" s="9" t="n"/>
-      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Room 6 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B27" s="54" t="n"/>
+          <t>Room 5 - Guest 1</t>
+        </is>
+      </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
         <is>
-          <t>Room 7 - Guest 1</t>
-        </is>
-      </c>
-      <c r="B28" s="54" t="n"/>
+          <t>Room 6 - Guest 1</t>
+        </is>
+      </c>
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
       <c r="G28" s="9" t="n"/>
-      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
-        <is>
-          <t>SECOND GUEST PER ROOM  -  only fill this block if two people share the room. FILLED counts occupied ROOMS, not guest names.</t>
-        </is>
-      </c>
+      <c r="A29" s="53" t="inlineStr">
+        <is>
+          <t>Room 7 - Guest 1</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="inlineStr">
-        <is>
-          <t>Room 1 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B30" s="54" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>SECOND GUEST PER ROOM  -  fill only if two people share the room. FILLED counts occupied ROOMS, not guest names.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Room 2 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B31" s="54" t="n"/>
+          <t>Room 1 - Guest 2</t>
+        </is>
+      </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="9" t="n"/>
       <c r="G31" s="9" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1" s="49">
+    <row r="32">
       <c r="A32" s="53" t="inlineStr">
         <is>
-          <t>Room 3 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B32" s="54" t="n"/>
+          <t>Room 2 - Guest 2</t>
+        </is>
+      </c>
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="9" t="n"/>
       <c r="G32" s="9" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1" s="49">
+    <row r="33">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Room 4 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B33" s="54" t="n"/>
+          <t>Room 3 - Guest 2</t>
+        </is>
+      </c>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="9" t="n"/>
       <c r="G33" s="9" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1" s="49">
+    <row r="34">
       <c r="A34" s="53" t="inlineStr">
         <is>
-          <t>Room 5 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B34" s="54" t="n"/>
+          <t>Room 4 - Guest 2</t>
+        </is>
+      </c>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1" s="49">
+    <row r="35">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Room 6 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B35" s="54" t="n"/>
+          <t>Room 5 - Guest 2</t>
+        </is>
+      </c>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1" s="49">
+    <row r="36">
       <c r="A36" s="53" t="inlineStr">
         <is>
-          <t>Room 7 - Guest 2</t>
-        </is>
-      </c>
-      <c r="B36" s="54" t="n"/>
+          <t>Room 6 - Guest 2</t>
+        </is>
+      </c>
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
@@ -1922,161 +2038,286 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="55" t="inlineStr">
+      <c r="A37" s="53" t="inlineStr">
+        <is>
+          <t>Room 7 - Guest 2</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
+        <is>
+          <t>THIRD GUEST PER ROOM  -  fill only if a THIRD person shares the room. These are the extra guests the hotel bills on top of the room rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="53" t="inlineStr">
+        <is>
+          <t>Room 1 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="53" t="inlineStr">
+        <is>
+          <t>Room 2 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="53" t="inlineStr">
+        <is>
+          <t>Room 3 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="53" t="inlineStr">
+        <is>
+          <t>Room 4 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="53" t="inlineStr">
+        <is>
+          <t>Room 5 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="53" t="inlineStr">
+        <is>
+          <t>Room 6 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="53" t="inlineStr">
+        <is>
+          <t>Room 7 - Guest 3</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="55" t="inlineStr">
         <is>
           <t>FILLED</t>
         </is>
       </c>
-      <c r="B37" s="54" t="n"/>
-      <c r="C37" s="9">
-        <f>SUMPRODUCT(--(((C22:C28&lt;&gt;"")+(C30:C36&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="D37" s="11">
-        <f>SUMPRODUCT(--(((D22:D28&lt;&gt;"")+(D30:D36&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="E37" s="11">
-        <f>SUMPRODUCT(--(((E22:E28&lt;&gt;"")+(E30:E36&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="F37" s="11">
-        <f>SUMPRODUCT(--(((F22:F28&lt;&gt;"")+(F30:F36&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-      <c r="G37" s="11">
-        <f>SUMPRODUCT(--(((G22:G28&lt;&gt;"")+(G30:G36&lt;&gt;""))&gt;0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="C46" s="9">
+        <f>SUMPRODUCT(--(((C23:C29&lt;&gt;"")+(C31:C37&lt;&gt;"")+(C39:C45&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="D46" s="9">
+        <f>SUMPRODUCT(--(((D23:D29&lt;&gt;"")+(D31:D37&lt;&gt;"")+(D39:D45&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="E46" s="9">
+        <f>SUMPRODUCT(--(((E23:E29&lt;&gt;"")+(E31:E37&lt;&gt;"")+(E39:E45&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="F46" s="9">
+        <f>SUMPRODUCT(--(((F23:F29&lt;&gt;"")+(F31:F37&lt;&gt;"")+(F39:F45&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="9">
+        <f>SUMPRODUCT(--(((G23:G29&lt;&gt;"")+(G31:G37&lt;&gt;"")+(G39:G45&lt;&gt;""))&gt;0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="55" t="inlineStr">
         <is>
           <t>NEEDED</t>
         </is>
       </c>
-      <c r="B38" s="54" t="n"/>
-      <c r="C38" s="9" t="n">
+      <c r="C47" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D47" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E47" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F47" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="55" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="B39" s="54" t="n"/>
-      <c r="C39" s="9">
-        <f>IF(C37=C38,"OK",IF(C37&lt;C38,"need "&amp;(C38-C37)&amp;" more","extra "&amp;(C37-C38)))</f>
-        <v/>
-      </c>
-      <c r="D39" s="4">
-        <f>IF(D37=D38,"OK",IF(D37&lt;D38,"need "&amp;(D38-D37)&amp;" more","extra "&amp;(D37-D38)))</f>
-        <v/>
-      </c>
-      <c r="E39" s="4">
-        <f>IF(E37=E38,"OK",IF(E37&lt;E38,"need "&amp;(E38-E37)&amp;" more","extra "&amp;(E37-E38)))</f>
-        <v/>
-      </c>
-      <c r="F39" s="4">
-        <f>IF(F37=F38,"OK",IF(F37&lt;F38,"need "&amp;(F38-F37)&amp;" more","extra "&amp;(F37-F38)))</f>
-        <v/>
-      </c>
-      <c r="G39" s="4">
-        <f>IF(G37=G38,"OK",IF(G37&lt;G38,"need "&amp;(G38-G37)&amp;" more","extra "&amp;(G37-G38)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="50" t="inlineStr">
+      <c r="C48">
+        <f>IF(C46=C47,"OK",IF(C46&lt;C47,"need "&amp;(C47-C46)&amp;" more","extra "&amp;(C46-C47)))</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>IF(D46=D47,"OK",IF(D46&lt;D47,"need "&amp;(D47-D46)&amp;" more","extra "&amp;(D46-D47)))</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>IF(E46=E47,"OK",IF(E46&lt;E47,"need "&amp;(E47-E46)&amp;" more","extra "&amp;(E46-E47)))</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>IF(F46=F47,"OK",IF(F46&lt;F47,"need "&amp;(F47-F46)&amp;" more","extra "&amp;(F46-F47)))</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>IF(G46=G47,"OK",IF(G46&lt;G47,"need "&amp;(G47-G46)&amp;" more","extra "&amp;(G46-G47)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="55" t="inlineStr">
+        <is>
+          <t>GUESTS</t>
+        </is>
+      </c>
+      <c r="C49" s="9">
+        <f>SUMPRODUCT(--(C23:C29&lt;&gt;""))+SUMPRODUCT(--(C31:C37&lt;&gt;""))+SUMPRODUCT(--(C39:C45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D49" s="9">
+        <f>SUMPRODUCT(--(D23:D29&lt;&gt;""))+SUMPRODUCT(--(D31:D37&lt;&gt;""))+SUMPRODUCT(--(D39:D45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="E49" s="9">
+        <f>SUMPRODUCT(--(E23:E29&lt;&gt;""))+SUMPRODUCT(--(E31:E37&lt;&gt;""))+SUMPRODUCT(--(E39:E45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="F49" s="9">
+        <f>SUMPRODUCT(--(F23:F29&lt;&gt;""))+SUMPRODUCT(--(F31:F37&lt;&gt;""))+SUMPRODUCT(--(F39:F45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G49" s="9">
+        <f>SUMPRODUCT(--(G23:G29&lt;&gt;""))+SUMPRODUCT(--(G31:G37&lt;&gt;""))+SUMPRODUCT(--(G39:G45&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>3rd GUESTS</t>
+        </is>
+      </c>
+      <c r="C50" s="9">
+        <f>SUMPRODUCT(--(C39:C45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D50" s="9">
+        <f>SUMPRODUCT(--(D39:D45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="E50" s="9">
+        <f>SUMPRODUCT(--(E39:E45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="F50" s="9">
+        <f>SUMPRODUCT(--(F39:F45&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G50" s="9">
+        <f>SUMPRODUCT(--(G39:G45&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="50" t="inlineStr">
         <is>
           <t>How to use:  every room has a 'Guest 1' row and a 'Guest 2' row. Type a name in the white cell for the night that guest is staying. Leave a cell blank if that guest is not in that room that night. FILLED counts occupied ROOMS, not guest names, so a room with two guests still counts as one room.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="50" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="50" t="inlineStr">
         <is>
           <t>Give this grid to the front desk on arrival. Hand out room keys against the names you typed.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="50" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="50" t="inlineStr">
         <is>
           <t>Two guests in one room?  Put the first name in the 'Guest 1' row and the second in the 'Guest 2' row for that same night. Both rows belong to the same room, so it still counts as one room against NEEDED.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="50" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="50" t="inlineStr">
         <is>
           <t>Checkout is 12-Dec at 12:30 PM, so 12-Dec needs 0 rooms overnight. Rooms 1-7 are held for the nights of 08, 09, 10 and 11 Dec only.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="50" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="50" t="inlineStr">
         <is>
           <t>Ask the front desk to release all 7 rooms on 12-Dec at 12:30 PM. Only 2 of the 7 rooms are actually needed on the night of 08-Dec.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A34:B34"/>
+  <mergeCells count="10">
+    <mergeCell ref="A56:AG56"/>
+    <mergeCell ref="A21:AG21"/>
+    <mergeCell ref="A53:AG53"/>
+    <mergeCell ref="A55:AG55"/>
+    <mergeCell ref="A12:AG12"/>
+    <mergeCell ref="A4:AG4"/>
+    <mergeCell ref="A38:AG38"/>
+    <mergeCell ref="A30:AG30"/>
+    <mergeCell ref="A54:AG54"/>
+    <mergeCell ref="A52:AG52"/>
   </mergeCells>
-  <conditionalFormatting sqref="C39:G39">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("need",D30))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>ISNUMBER(SEARCH("over",D30))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2111,7 +2352,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="49">
       <c r="A3" s="12" t="inlineStr">
         <is>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -843,6 +843,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -904,6 +905,7 @@
         <v>37</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="48" t="inlineStr">
         <is>
@@ -994,6 +996,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
         <is>
@@ -1672,6 +1675,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -1745,6 +1749,7 @@
         <v>23</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="48" t="inlineStr">
         <is>
@@ -1825,6 +1830,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
         <is>
@@ -2352,6 +2358,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="49">
       <c r="A3" s="12" t="inlineStr">
         <is>
@@ -2500,7 +2507,7 @@
       </c>
       <c r="Q4" s="16" t="inlineStr">
         <is>
-          <t>11-Dec-2026, 7:00-10:00 PM.  Single combined row for the whole invoice: DJ mixer + operator, 4 top &amp; 2 bass speakers, mic, paar lights, name board both sides, driver, fuel, dance floor, light umbrella setup, generator backup, Punjabi dhol x2.  Do not add separate lighting, DJ or generator rows - all of it is inside the 41,000.  See the itemised reference further down.</t>
+          <t>11-Dec-2026, 7:00-10:00 PM.  Single combined row for the whole invoice: DJ mixer + operator, 4 top &amp; 2 bass speakers, mic, paar lights, name board both sides, driver, fuel, dance floor, light umbrella setup, generator backup, Punjabi dhol x2.  Do not add separate lighting, DJ or generator rows - all of it is inside the 41,000.  See the itemised reference further down. [SYNC-CHECK-20261004-1206]</t>
         </is>
       </c>
     </row>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2507,7 +2507,7 @@
       </c>
       <c r="Q4" s="16" t="inlineStr">
         <is>
-          <t>11-Dec-2026, 7:00-10:00 PM.  Single combined row for the whole invoice: DJ mixer + operator, 4 top &amp; 2 bass speakers, mic, paar lights, name board both sides, driver, fuel, dance floor, light umbrella setup, generator backup, Punjabi dhol x2.  Do not add separate lighting, DJ or generator rows - all of it is inside the 41,000.  See the itemised reference further down. [SYNC-CHECK-20261004-1206]</t>
+          <t>11-Dec-2026, 7:00-10:00 PM.  Single combined row for the whole invoice: DJ mixer + operator, 4 top &amp; 2 bass speakers, mic, paar lights, name board both sides, driver, fuel, dance floor, light umbrella setup, generator backup, Punjabi dhol x2.  Do not add separate lighting, DJ or generator rows - all of it is inside the 41,000.  See the itemised reference further down.</t>
         </is>
       </c>
     </row>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1057,7 +1057,11 @@
           <t>Room 1 - Guest 1</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -1331,7 +1335,11 @@
           <t>Room 1 - Guest 3</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1198,7 +1198,11 @@
           <t>Room 1 - Guest 2</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Suraj</t>
+        </is>
+      </c>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1057,11 +1057,7 @@
           <t>Room 1 - Guest 1</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Hello</t>
-        </is>
-      </c>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -1198,11 +1194,7 @@
           <t>Room 1 - Guest 2</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Suraj</t>
-        </is>
-      </c>
+      <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
@@ -1339,11 +1331,7 @@
           <t>Room 1 - Guest 3</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Hi</t>
-        </is>
-      </c>
+      <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1057,7 +1057,11 @@
           <t>Room 1 - Guest 1</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Suraj</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -1198,7 +1198,11 @@
           <t>Room 1 - Guest 2</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Smolly</t>
+        </is>
+      </c>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1339,7 +1339,11 @@
           <t>Room 1 - Guest 3</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1339,11 +1339,7 @@
           <t>Room 1 - Guest 3</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
+      <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1088,7 +1088,11 @@
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Raghav</t>
+        </is>
+      </c>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -1107,7 +1107,11 @@
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Sunny</t>
+        </is>
+      </c>
       <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n"/>
     </row>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2600,11 +2600,19 @@
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Photography</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr"/>
+          <t>Photography &amp; Videography</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>9763002700</t>
+        </is>
+      </c>
       <c r="D7" s="23" t="inlineStr"/>
       <c r="E7" s="24" t="n"/>
       <c r="F7" s="25" t="inlineStr"/>
@@ -2618,8 +2626,12 @@
           <t>12-Dec-2026</t>
         </is>
       </c>
-      <c r="I7" s="28" t="n"/>
-      <c r="J7" s="28" t="n"/>
+      <c r="I7" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="29">
         <f>IF(I7="","",I7-IF(J7="",0,J7))</f>
         <v/>
@@ -2632,7 +2644,11 @@
         <v/>
       </c>
       <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="25" t="inlineStr"/>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t>Total 118, Priyanka will pay 80 rest will be paid by me</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2986,11 +2986,19 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Other / Miscellaneous</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr"/>
-      <c r="C17" s="22" t="inlineStr"/>
+          <t>Car Booking</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>Zippy Car Rental-Self Drive Cars</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>+91 99212 08410</t>
+        </is>
+      </c>
       <c r="D17" s="23" t="inlineStr"/>
       <c r="E17" s="24" t="n"/>
       <c r="F17" s="25" t="inlineStr"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2618,7 +2618,7 @@
       <c r="F7" s="25" t="inlineStr"/>
       <c r="G7" s="26" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>All events</t>
         </is>
       </c>
       <c r="H7" s="27" t="inlineStr">
@@ -2949,17 +2949,21 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Sangeet Anchoring / Choreography</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr"/>
+          <t>Safa Wala</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Feta by Rohit</t>
+        </is>
+      </c>
       <c r="C16" s="22" t="inlineStr"/>
       <c r="D16" s="23" t="inlineStr"/>
       <c r="E16" s="24" t="n"/>
       <c r="F16" s="25" t="inlineStr"/>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>Sangeet Night</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -3002,7 +3006,11 @@
       <c r="D17" s="23" t="inlineStr"/>
       <c r="E17" s="24" t="n"/>
       <c r="F17" s="25" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>All events</t>
+        </is>
+      </c>
       <c r="H17" s="14" t="inlineStr"/>
       <c r="I17" s="28" t="n"/>
       <c r="J17" s="28" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="57" t="inlineStr">
         <is>
-          <t>+91?93091?74167</t>
+          <t>+919309174167</t>
         </is>
       </c>
       <c r="E18" s="24" t="n"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2957,7 +2957,11 @@
           <t>Feta by Rohit</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr"/>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>09270236512</t>
+        </is>
+      </c>
       <c r="D16" s="23" t="inlineStr"/>
       <c r="E16" s="24" t="n"/>
       <c r="F16" s="25" t="inlineStr"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="16" t="inlineStr"/>
       <c r="I18" s="14" t="n">
-        <v>84000</v>
+        <v>93000</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>25000</v>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2994,7 +2994,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Car Booking</t>
+          <t>Car Booking_1</t>
         </is>
       </c>
       <c r="B17" s="21" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>+91 99212 08410</t>
+          <t>+919921208410</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr"/>
@@ -3016,7 +3016,9 @@
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr"/>
-      <c r="I17" s="28" t="n"/>
+      <c r="I17" s="28" t="n">
+        <v>41600</v>
+      </c>
       <c r="J17" s="28" t="n"/>
       <c r="K17" s="17">
         <f>IF(I17="","",I17-IF(J17="",0,J17))</f>
@@ -3030,7 +3032,11 @@
         <v/>
       </c>
       <c r="P17" s="25" t="n"/>
-      <c r="Q17" s="25" t="inlineStr"/>
+      <c r="Q17" s="25" t="inlineStr">
+        <is>
+          <t>? Brezza Self Drive: 08?14 Dec | ?2,300/day  ? Ertiga with Driver: 08?13 Dec | ?4,250/day</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="75" customHeight="1" s="49">
       <c r="A18" s="38" t="inlineStr">

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -3089,7 +3089,11 @@
         <v/>
       </c>
       <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="46" t="inlineStr"/>
+      <c r="Q18" s="46" t="inlineStr">
+        <is>
+          <t>Total 41 Rooms @ Rs 2270 /Day</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2975,7 +2975,9 @@
           <t>11-Dec-2026</t>
         </is>
       </c>
-      <c r="I16" s="28" t="n"/>
+      <c r="I16" s="28" t="n">
+        <v>6200</v>
+      </c>
       <c r="J16" s="28" t="n"/>
       <c r="K16" s="17">
         <f>IF(I16="","",I16-IF(J16="",0,J16))</f>
@@ -2989,7 +2991,11 @@
         <v/>
       </c>
       <c r="P16" s="25" t="n"/>
-      <c r="Q16" s="25" t="inlineStr"/>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t>Rs 5000 for 50 Person and Rs 1200 for Groom</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2350,7 +2350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" style="49" min="1" max="1"/>
@@ -3102,147 +3102,182 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>IRCTC Bookings</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr"/>
+      <c r="C19" s="39" t="inlineStr"/>
+      <c r="D19" s="57" t="inlineStr"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="40" t="inlineStr"/>
+      <c r="G19" s="41" t="inlineStr"/>
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K19" s="17">
+        <f>IF(I19="","",I19-IF(J19="",0,J19))</f>
+        <v/>
+      </c>
+      <c r="L19" s="17" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+      <c r="N19" s="14" t="inlineStr"/>
+      <c r="O19" s="18">
+        <f>IF(I19="","Not Quoted",IF(K19&lt;=0,"Paid","Pending"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="46" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="33">
-        <f>SUM(I4:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="33">
-        <f>SUM(J4:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="33">
-        <f>SUM(K4:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="33">
+        <f>SUM(I4:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="33">
+        <f>SUM(J4:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="33">
+        <f>SUM(K4:K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="32" t="n"/>
+      <c r="M20" s="32" t="n"/>
+      <c r="N20" s="32" t="n"/>
+      <c r="O20" s="32" t="n"/>
+      <c r="P20" s="32" t="n"/>
+      <c r="Q20" s="32" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>PAYMENT SUMMARY</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Total quoted</t>
-        </is>
-      </c>
-      <c r="B22" s="34">
-        <f>I19</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Total paid</t>
+          <t>Total quoted</t>
         </is>
       </c>
       <c r="B23" s="34">
-        <f>J19</f>
+        <f>I19</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Total outstanding</t>
+          <t>Total paid</t>
         </is>
       </c>
       <c r="B24" s="34">
-        <f>K19</f>
+        <f>J19</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Vendors still pending</t>
-        </is>
-      </c>
-      <c r="B25" s="35">
-        <f>COUNTIF(O4:O18,"Pending")</f>
+          <t>Total outstanding</t>
+        </is>
+      </c>
+      <c r="B25" s="34">
+        <f>K19</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Vendors fully paid</t>
+          <t>Vendors still pending</t>
         </is>
       </c>
       <c r="B26" s="35">
-        <f>COUNTIF(O4:O18,"Paid")</f>
+        <f>COUNTIF(O4:O18,"Pending")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>Vendors fully paid</t>
+        </is>
+      </c>
+      <c r="B27" s="35">
+        <f>COUNTIF(O4:O18,"Paid")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Not quoted yet</t>
         </is>
       </c>
-      <c r="B27" s="35">
+      <c r="B28" s="35">
         <f>COUNTIF(O4:O18,"Not Quoted")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="50" t="inlineStr">
-        <is>
-          <t>Status is automatic:  no amount yet -&gt; Not Quoted  |  balance cleared -&gt; Paid  |  balance left -&gt; Pending.  Filter column O to see who still owes money.</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="50" t="inlineStr">
         <is>
-          <t>Quote PDF links to the invoice file. Drop new invoices in the 'Vendor PDFs' folder next to this workbook and link them the same way. Keep the folder together with the workbook or the links break.</t>
+          <t>Status is automatic:  no amount yet -&gt; Not Quoted  |  balance cleared -&gt; Paid  |  balance left -&gt; Pending.  Filter column O to see who still owes money.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="inlineStr">
         <is>
-          <t>Invoice terms for each vendor are on that vendor's own sheet, e.g. 'Deeplaxmie Events'.</t>
+          <t>Quote PDF links to the invoice file. Drop new invoices in the 'Vendor PDFs' folder next to this workbook and link them the same way. Keep the folder together with the workbook or the links break.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="inlineStr">
         <is>
-          <t>Rule: one row per vendor.  Never split one invoice into several vendor rows - if a single invoice covers DJ, sound, lighting and generator, all of it belongs in that one vendor's row and that one total.  Add a new row only for a genuinely new vendor.</t>
+          <t>Invoice terms for each vendor are on that vendor's own sheet, e.g. 'Deeplaxmie Events'.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="inlineStr">
         <is>
+          <t>Rule: one row per vendor.  Never split one invoice into several vendor rows - if a single invoice covers DJ, sound, lighting and generator, all of it belongs in that one vendor's row and that one total.  Add a new row only for a genuinely new vendor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="50" t="inlineStr">
+        <is>
           <t>Extracted invoice line items live on that vendor's own sheet - one sheet per vendor.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="50" t="n"/>
+    <row r="35">
+      <c r="A35" s="50" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1" s="49"/>
     <row r="40" ht="24" customHeight="1" s="49"/>

--- a/Wedding_Expense_Tracker_Dec2026.xlsx
+++ b/Wedding_Expense_Tracker_Dec2026.xlsx
@@ -2350,7 +2350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" style="49" min="1" max="1"/>
@@ -2774,7 +2774,7 @@
       <c r="F11" s="25" t="inlineStr"/>
       <c r="G11" s="26" t="inlineStr">
         <is>
-          <t>Mehendi</t>
+          <t>Baraat</t>
         </is>
       </c>
       <c r="H11" s="27" t="inlineStr">
@@ -3135,149 +3135,182 @@
       <c r="Q19" s="46" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>IRCTC Bookings</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr"/>
+      <c r="C20" s="39" t="inlineStr"/>
+      <c r="D20" s="57" t="inlineStr"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="40" t="inlineStr"/>
+      <c r="G20" s="41" t="inlineStr"/>
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K20" s="17">
+        <f>IF(I20="","",I20-IF(J20="",0,J20))</f>
+        <v/>
+      </c>
+      <c r="L20" s="17" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+      <c r="N20" s="14" t="inlineStr"/>
+      <c r="O20" s="18">
+        <f>IF(I20="","Not Quoted",IF(K20&lt;=0,"Paid","Pending"))</f>
+        <v/>
+      </c>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="46" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="32" t="n"/>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="33">
-        <f>SUM(I4:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="33">
-        <f>SUM(J4:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="33">
-        <f>SUM(K4:K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
-      <c r="O20" s="32" t="n"/>
-      <c r="P20" s="32" t="n"/>
-      <c r="Q20" s="32" t="n"/>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="33">
+        <f>SUM(I4:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="33">
+        <f>SUM(J4:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="33">
+        <f>SUM(K4:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="32" t="n"/>
+      <c r="M21" s="32" t="n"/>
+      <c r="N21" s="32" t="n"/>
+      <c r="O21" s="32" t="n"/>
+      <c r="P21" s="32" t="n"/>
+      <c r="Q21" s="32" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>PAYMENT SUMMARY</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Total quoted</t>
-        </is>
-      </c>
-      <c r="B23" s="34">
-        <f>I19</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Total paid</t>
+          <t>Total quoted</t>
         </is>
       </c>
       <c r="B24" s="34">
-        <f>J19</f>
+        <f>I19</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total outstanding</t>
+          <t>Total paid</t>
         </is>
       </c>
       <c r="B25" s="34">
-        <f>K19</f>
+        <f>J19</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Vendors still pending</t>
-        </is>
-      </c>
-      <c r="B26" s="35">
-        <f>COUNTIF(O4:O18,"Pending")</f>
+          <t>Total outstanding</t>
+        </is>
+      </c>
+      <c r="B26" s="34">
+        <f>K19</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Vendors fully paid</t>
+          <t>Vendors still pending</t>
         </is>
       </c>
       <c r="B27" s="35">
-        <f>COUNTIF(O4:O18,"Paid")</f>
+        <f>COUNTIF(O4:O18,"Pending")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>Vendors fully paid</t>
+        </is>
+      </c>
+      <c r="B28" s="35">
+        <f>COUNTIF(O4:O18,"Paid")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>Not quoted yet</t>
         </is>
       </c>
-      <c r="B28" s="35">
+      <c r="B29" s="35">
         <f>COUNTIF(O4:O18,"Not Quoted")</f>
         <v/>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="50" t="inlineStr">
-        <is>
-          <t>Status is automatic:  no amount yet -&gt; Not Quoted  |  balance cleared -&gt; Paid  |  balance left -&gt; Pending.  Filter column O to see who still owes money.</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="50" t="inlineStr">
         <is>
-          <t>Quote PDF links to the invoice file. Drop new invoices in the 'Vendor PDFs' folder next to this workbook and link them the same way. Keep the folder together with the workbook or the links break.</t>
+          <t>Status is automatic:  no amount yet -&gt; Not Quoted  |  balance cleared -&gt; Paid  |  balance left -&gt; Pending.  Filter column O to see who still owes money.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="inlineStr">
         <is>
-          <t>Invoice terms for each vendor are on that vendor's own sheet, e.g. 'Deeplaxmie Events'.</t>
+          <t>Quote PDF links to the invoice file. Drop new invoices in the 'Vendor PDFs' folder next to this workbook and link them the same way. Keep the folder together with the workbook or the links break.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="inlineStr">
         <is>
-          <t>Rule: one row per vendor.  Never split one invoice into several vendor rows - if a single invoice covers DJ, sound, lighting and generator, all of it belongs in that one vendor's row and that one total.  Add a new row only for a genuinely new vendor.</t>
+          <t>Invoice terms for each vendor are on that vendor's own sheet, e.g. 'Deeplaxmie Events'.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50" t="inlineStr">
         <is>
+          <t>Rule: one row per vendor.  Never split one invoice into several vendor rows - if a single invoice covers DJ, sound, lighting and generator, all of it belongs in that one vendor's row and that one total.  Add a new row only for a genuinely new vendor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
           <t>Extracted invoice line items live on that vendor's own sheet - one sheet per vendor.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="50" t="n"/>
+    <row r="36">
+      <c r="A36" s="50" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1" s="49"/>
     <row r="40" ht="24" customHeight="1" s="49"/>
